--- a/artfynd/A 60585-2024 artfynd.xlsx
+++ b/artfynd/A 60585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129530349</v>
       </c>
       <c r="B2" t="n">
-        <v>56660</v>
+        <v>56663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60585-2024 artfynd.xlsx
+++ b/artfynd/A 60585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129530349</v>
       </c>
       <c r="B2" t="n">
-        <v>56663</v>
+        <v>56668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60585-2024 artfynd.xlsx
+++ b/artfynd/A 60585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129530349</v>
       </c>
       <c r="B2" t="n">
-        <v>56668</v>
+        <v>56669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60585-2024 artfynd.xlsx
+++ b/artfynd/A 60585-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129530349</v>
       </c>
       <c r="B2" t="n">
-        <v>56669</v>
+        <v>56884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
